--- a/artfynd/A 62137-2025 artfynd.xlsx
+++ b/artfynd/A 62137-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1407,6 +1407,849 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130217837</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90673</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>S L. Hedningen, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>630384</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6555213</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130217841</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>S L. Hedningen, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>630608</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6555276</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130217842</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>S L. Hedningen, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>630475</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6555308</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130217846</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96429</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>S L. Hedningen, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>630670</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6555276</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130217838</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56931</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>S L. Hedningen, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>630693</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6555135</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130217847</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8440</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>S L. Hedningen, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>630458</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6555201</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130217836</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79714</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>S L. Hedningen, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>630607</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6555136</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130217843</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98833</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>S L. Hedningen, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>630369</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6555254</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>24 skott och två fröställningar</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62137-2025 artfynd.xlsx
+++ b/artfynd/A 62137-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130181270</v>
+        <v>130181272</v>
       </c>
       <c r="B2" t="n">
-        <v>8451</v>
+        <v>43995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>101735</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>630312</v>
+        <v>630527</v>
       </c>
       <c r="R2" t="n">
-        <v>6555306</v>
+        <v>6555290</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130181272</v>
+        <v>130181270</v>
       </c>
       <c r="B3" t="n">
-        <v>43995</v>
+        <v>8451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101735</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>630527</v>
+        <v>630312</v>
       </c>
       <c r="R3" t="n">
-        <v>6555290</v>
+        <v>6555306</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1108,7 +1108,7 @@
         <v>130181267</v>
       </c>
       <c r="B6" t="n">
-        <v>91660</v>
+        <v>91662</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>130181273</v>
       </c>
       <c r="B7" t="n">
-        <v>96273</v>
+        <v>96275</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>130181266</v>
       </c>
       <c r="B8" t="n">
-        <v>91660</v>
+        <v>91662</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 62137-2025 artfynd.xlsx
+++ b/artfynd/A 62137-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130181272</v>
+        <v>130181270</v>
       </c>
       <c r="B2" t="n">
-        <v>43995</v>
+        <v>8451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101735</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>630527</v>
+        <v>630312</v>
       </c>
       <c r="R2" t="n">
-        <v>6555290</v>
+        <v>6555306</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130181270</v>
+        <v>130181272</v>
       </c>
       <c r="B3" t="n">
-        <v>8451</v>
+        <v>44080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>101735</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>630312</v>
+        <v>630527</v>
       </c>
       <c r="R3" t="n">
-        <v>6555306</v>
+        <v>6555290</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
         <v>130181268</v>
       </c>
       <c r="B5" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>130181267</v>
       </c>
       <c r="B6" t="n">
-        <v>91662</v>
+        <v>91749</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>130181273</v>
       </c>
       <c r="B7" t="n">
-        <v>96275</v>
+        <v>96362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>130181266</v>
       </c>
       <c r="B8" t="n">
-        <v>91662</v>
+        <v>91749</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>130217837</v>
       </c>
       <c r="B9" t="n">
-        <v>90673</v>
+        <v>90760</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>130217846</v>
       </c>
       <c r="B12" t="n">
-        <v>96429</v>
+        <v>96516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>130217838</v>
       </c>
       <c r="B13" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>130217836</v>
       </c>
       <c r="B15" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>130217843</v>
       </c>
       <c r="B16" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 62137-2025 artfynd.xlsx
+++ b/artfynd/A 62137-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130181270</v>
+        <v>130181272</v>
       </c>
       <c r="B2" t="n">
-        <v>8451</v>
+        <v>44080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>101735</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>630312</v>
+        <v>630527</v>
       </c>
       <c r="R2" t="n">
-        <v>6555306</v>
+        <v>6555290</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130181272</v>
+        <v>130181270</v>
       </c>
       <c r="B3" t="n">
-        <v>44080</v>
+        <v>8451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101735</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>630527</v>
+        <v>630312</v>
       </c>
       <c r="R3" t="n">
-        <v>6555290</v>
+        <v>6555306</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 62137-2025 artfynd.xlsx
+++ b/artfynd/A 62137-2025 artfynd.xlsx
@@ -1105,45 +1105,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130181267</v>
+        <v>130181273</v>
       </c>
       <c r="B6" t="n">
-        <v>91749</v>
+        <v>96362</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>S L. Hedningen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630304</v>
+        <v>630291</v>
       </c>
       <c r="R6" t="n">
-        <v>6555329</v>
+        <v>6555405</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,6 +1196,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1202,57 +1215,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130181273</v>
+        <v>130181267</v>
       </c>
       <c r="B7" t="n">
-        <v>96362</v>
+        <v>91749</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>S L. Hedningen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630291</v>
+        <v>630304</v>
       </c>
       <c r="R7" t="n">
-        <v>6555405</v>
+        <v>6555329</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,7 +1294,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 62137-2025 artfynd.xlsx
+++ b/artfynd/A 62137-2025 artfynd.xlsx
@@ -1105,57 +1105,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130181273</v>
+        <v>130181267</v>
       </c>
       <c r="B6" t="n">
-        <v>96362</v>
+        <v>91752</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>S L. Hedningen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630291</v>
+        <v>630304</v>
       </c>
       <c r="R6" t="n">
-        <v>6555405</v>
+        <v>6555329</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,7 +1184,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1215,45 +1202,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130181267</v>
+        <v>130181273</v>
       </c>
       <c r="B7" t="n">
-        <v>91749</v>
+        <v>96365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>S L. Hedningen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630304</v>
+        <v>630291</v>
       </c>
       <c r="R7" t="n">
-        <v>6555329</v>
+        <v>6555405</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,6 +1293,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>130181266</v>
       </c>
       <c r="B8" t="n">
-        <v>91749</v>
+        <v>91752</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>130217837</v>
       </c>
       <c r="B9" t="n">
-        <v>90760</v>
+        <v>90763</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>130217846</v>
       </c>
       <c r="B12" t="n">
-        <v>96516</v>
+        <v>96519</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>130217836</v>
       </c>
       <c r="B15" t="n">
-        <v>79799</v>
+        <v>79802</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>130217843</v>
       </c>
       <c r="B16" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 62137-2025 artfynd.xlsx
+++ b/artfynd/A 62137-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130181272</v>
       </c>
       <c r="B2" t="n">
-        <v>44080</v>
+        <v>44106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130181268</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>130181267</v>
       </c>
       <c r="B6" t="n">
-        <v>91752</v>
+        <v>91778</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>130181273</v>
       </c>
       <c r="B7" t="n">
-        <v>96365</v>
+        <v>96391</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>130181266</v>
       </c>
       <c r="B8" t="n">
-        <v>91752</v>
+        <v>91778</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>130217837</v>
       </c>
       <c r="B9" t="n">
-        <v>90763</v>
+        <v>90789</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>130217846</v>
       </c>
       <c r="B12" t="n">
-        <v>96519</v>
+        <v>96545</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>130217838</v>
       </c>
       <c r="B13" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>130217836</v>
       </c>
       <c r="B15" t="n">
-        <v>79802</v>
+        <v>79828</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>130217843</v>
       </c>
       <c r="B16" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 62137-2025 artfynd.xlsx
+++ b/artfynd/A 62137-2025 artfynd.xlsx
@@ -1105,45 +1105,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130181267</v>
+        <v>130181273</v>
       </c>
       <c r="B6" t="n">
-        <v>91778</v>
+        <v>96391</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>S L. Hedningen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630304</v>
+        <v>630291</v>
       </c>
       <c r="R6" t="n">
-        <v>6555329</v>
+        <v>6555405</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,6 +1196,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1202,57 +1215,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130181273</v>
+        <v>130181267</v>
       </c>
       <c r="B7" t="n">
-        <v>96391</v>
+        <v>91778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>S L. Hedningen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630291</v>
+        <v>630304</v>
       </c>
       <c r="R7" t="n">
-        <v>6555405</v>
+        <v>6555329</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,7 +1294,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 62137-2025 artfynd.xlsx
+++ b/artfynd/A 62137-2025 artfynd.xlsx
@@ -1105,57 +1105,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130181273</v>
+        <v>130181267</v>
       </c>
       <c r="B6" t="n">
-        <v>96391</v>
+        <v>91779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>S L. Hedningen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630291</v>
+        <v>630304</v>
       </c>
       <c r="R6" t="n">
-        <v>6555405</v>
+        <v>6555329</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,7 +1184,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1215,45 +1202,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130181267</v>
+        <v>130181273</v>
       </c>
       <c r="B7" t="n">
-        <v>91778</v>
+        <v>96392</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>S L. Hedningen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630304</v>
+        <v>630291</v>
       </c>
       <c r="R7" t="n">
-        <v>6555329</v>
+        <v>6555405</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,6 +1293,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>130181266</v>
       </c>
       <c r="B8" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>130217837</v>
       </c>
       <c r="B9" t="n">
-        <v>90789</v>
+        <v>90790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>130217846</v>
       </c>
       <c r="B12" t="n">
-        <v>96545</v>
+        <v>96546</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>130217843</v>
       </c>
       <c r="B16" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 62137-2025 artfynd.xlsx
+++ b/artfynd/A 62137-2025 artfynd.xlsx
@@ -1105,45 +1105,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130181267</v>
+        <v>130181273</v>
       </c>
       <c r="B6" t="n">
-        <v>91779</v>
+        <v>96393</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>S L. Hedningen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630304</v>
+        <v>630291</v>
       </c>
       <c r="R6" t="n">
-        <v>6555329</v>
+        <v>6555405</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,6 +1196,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1202,57 +1215,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130181273</v>
+        <v>130181267</v>
       </c>
       <c r="B7" t="n">
-        <v>96392</v>
+        <v>91780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>S L. Hedningen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630291</v>
+        <v>630304</v>
       </c>
       <c r="R7" t="n">
-        <v>6555405</v>
+        <v>6555329</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,7 +1294,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>130181266</v>
       </c>
       <c r="B8" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>130217837</v>
       </c>
       <c r="B9" t="n">
-        <v>90790</v>
+        <v>90791</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>130217846</v>
       </c>
       <c r="B12" t="n">
-        <v>96546</v>
+        <v>96547</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>130217843</v>
       </c>
       <c r="B16" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 62137-2025 artfynd.xlsx
+++ b/artfynd/A 62137-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130181272</v>
       </c>
       <c r="B2" t="n">
-        <v>44106</v>
+        <v>44108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130181268</v>
       </c>
       <c r="B5" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>130181273</v>
       </c>
       <c r="B6" t="n">
-        <v>96393</v>
+        <v>96395</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>130181267</v>
       </c>
       <c r="B7" t="n">
-        <v>91780</v>
+        <v>91782</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>130181266</v>
       </c>
       <c r="B8" t="n">
-        <v>91780</v>
+        <v>91782</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>130217837</v>
       </c>
       <c r="B9" t="n">
-        <v>90791</v>
+        <v>90793</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>130217846</v>
       </c>
       <c r="B12" t="n">
-        <v>96547</v>
+        <v>96549</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>130217838</v>
       </c>
       <c r="B13" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>130217836</v>
       </c>
       <c r="B15" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>130217843</v>
       </c>
       <c r="B16" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 62137-2025 artfynd.xlsx
+++ b/artfynd/A 62137-2025 artfynd.xlsx
@@ -1105,57 +1105,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130181273</v>
+        <v>130181267</v>
       </c>
       <c r="B6" t="n">
-        <v>96395</v>
+        <v>91782</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>S L. Hedningen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630291</v>
+        <v>630304</v>
       </c>
       <c r="R6" t="n">
-        <v>6555405</v>
+        <v>6555329</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,7 +1184,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1215,45 +1202,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130181267</v>
+        <v>130181273</v>
       </c>
       <c r="B7" t="n">
-        <v>91782</v>
+        <v>96399</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>S L. Hedningen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630304</v>
+        <v>630291</v>
       </c>
       <c r="R7" t="n">
-        <v>6555329</v>
+        <v>6555405</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,6 +1293,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1730,7 +1730,7 @@
         <v>130217846</v>
       </c>
       <c r="B12" t="n">
-        <v>96549</v>
+        <v>96553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>130217843</v>
       </c>
       <c r="B16" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 62137-2025 artfynd.xlsx
+++ b/artfynd/A 62137-2025 artfynd.xlsx
@@ -1827,7 +1827,7 @@
         <v>130217838</v>
       </c>
       <c r="B13" t="n">
-        <v>57044</v>
+        <v>57053</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
